--- a/Outputs/Scenarios/PtX_demand_SE_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SE_Electrification.xlsx
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.005820828635756495</v>
+        <v>0.005820828635756494</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0003480071404518354</v>
       </c>
       <c r="K42" t="n">
-        <v>0.005820828635756495</v>
+        <v>0.005820828635756494</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_SE_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SE_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.004466517697420779</v>
       </c>
       <c r="K16" t="n">
-        <v>0.005941527048797491</v>
+        <v>0.006475259306487511</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0009902545081329152</v>
+        <v>0.001296853546147529</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.003961018032531661</v>
+        <v>0.005187414184590114</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.005941527048797491</v>
+        <v>0.005187414184590114</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.000357947561235644</v>
       </c>
       <c r="K24" t="n">
-        <v>0.008286954986202369</v>
+        <v>0.008135779775790603</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.002166657341216589</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08047330113284328</v>
+        <v>0.0790052627216847</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>6.435495947338796e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0009902545081329152</v>
+        <v>0.001296853546147529</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006612135668584872</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03492497181453896</v>
+        <v>0.03489260992563982</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.005820828635756494</v>
+        <v>0.006988230551797707</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02328331454302598</v>
+        <v>0.02795292220719083</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03492497181453896</v>
+        <v>0.02795292220719083</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0003480071404518354</v>
       </c>
       <c r="K42" t="n">
-        <v>0.005820828635756494</v>
+        <v>0.006988230551797707</v>
       </c>
     </row>
     <row r="43">
